--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/TENNESSEE_2019.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2019/TENNESSEE_2019.xlsx
@@ -3318,7 +3318,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C165">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C272">
@@ -13182,7 +13182,7 @@
       </c>
       <c r="B713" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C713">
@@ -13200,7 +13200,7 @@
       </c>
       <c r="B714" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C714">
@@ -13758,7 +13758,7 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C745">
@@ -13776,7 +13776,7 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C746">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C750">
